--- a/Put Transactions.xlsx
+++ b/Put Transactions.xlsx
@@ -27,7 +27,7 @@
     <numFmt numFmtId="169" formatCode="0.0%"/>
     <numFmt numFmtId="170" formatCode="$#,##0.00"/>
   </numFmts>
-  <fonts count="24">
+  <fonts count="32">
     <font>
       <name val="Aptos Narrow"/>
       <family val="2"/>
@@ -171,8 +171,56 @@
       <color rgb="FFFFFFFF"/>
       <sz val="11"/>
     </font>
+    <font>
+      <name val="Arial"/>
+      <b val="1"/>
+      <color rgb="00FFFFFF"/>
+      <sz val="20"/>
+    </font>
+    <font>
+      <name val="Arial"/>
+      <i val="1"/>
+      <color rgb="00666666"/>
+      <sz val="10"/>
+    </font>
+    <font>
+      <name val="Arial"/>
+      <b val="1"/>
+      <color rgb="00FFFFFF"/>
+      <sz val="16"/>
+    </font>
+    <font>
+      <name val="Arial"/>
+      <b val="1"/>
+      <color rgb="00FFFFFF"/>
+      <sz val="12"/>
+    </font>
+    <font>
+      <name val="Arial"/>
+      <b val="1"/>
+      <color rgb="00FFFFFF"/>
+      <sz val="13"/>
+    </font>
+    <font>
+      <name val="Arial"/>
+      <b val="1"/>
+      <color rgb="001F4E79"/>
+      <sz val="11"/>
+    </font>
+    <font>
+      <name val="Arial"/>
+      <b val="1"/>
+      <color rgb="00FFFFFF"/>
+      <sz val="14"/>
+    </font>
+    <font>
+      <name val="Arial"/>
+      <b val="1"/>
+      <color rgb="00FFFFFF"/>
+      <sz val="11"/>
+    </font>
   </fonts>
-  <fills count="13">
+  <fills count="24">
     <fill>
       <patternFill/>
     </fill>
@@ -245,8 +293,74 @@
         <bgColor rgb="FF9C27B0"/>
       </patternFill>
     </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="001F4E79"/>
+        <bgColor rgb="001F4E79"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="004CAF50"/>
+        <bgColor rgb="004CAF50"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="002196F3"/>
+        <bgColor rgb="002196F3"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="00F44336"/>
+        <bgColor rgb="00F44336"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="00FF9800"/>
+        <bgColor rgb="00FF9800"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="00E91E63"/>
+        <bgColor rgb="00E91E63"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="00607D8B"/>
+        <bgColor rgb="00607D8B"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="00F8F9FA"/>
+        <bgColor rgb="00F8F9FA"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="00E3F2FD"/>
+        <bgColor rgb="00E3F2FD"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="00E8F5E8"/>
+        <bgColor rgb="00E8F5E8"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="009C27B0"/>
+        <bgColor rgb="009C27B0"/>
+      </patternFill>
+    </fill>
   </fills>
-  <borders count="7">
+  <borders count="12">
     <border>
       <left/>
       <right/>
@@ -328,12 +442,46 @@
       <bottom/>
       <diagonal/>
     </border>
+    <border>
+      <left style="thin"/>
+      <right style="thin"/>
+      <top style="thin"/>
+      <bottom style="thin"/>
+    </border>
+    <border>
+      <left/>
+      <right/>
+      <top style="thin"/>
+      <bottom/>
+      <diagonal/>
+    </border>
+    <border>
+      <left/>
+      <right style="thin"/>
+      <top style="thin"/>
+      <bottom/>
+      <diagonal/>
+    </border>
+    <border>
+      <left/>
+      <right/>
+      <top style="thin"/>
+      <bottom style="thin"/>
+      <diagonal/>
+    </border>
+    <border>
+      <left/>
+      <right style="thin"/>
+      <top style="thin"/>
+      <bottom style="thin"/>
+      <diagonal/>
+    </border>
   </borders>
   <cellStyleXfs count="2">
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0"/>
     <xf numFmtId="9" fontId="1" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="97">
+  <cellXfs count="118">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="2" fillId="0" borderId="1" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="14" fontId="2" fillId="0" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
@@ -503,6 +651,43 @@
     <xf numFmtId="168" fontId="21" fillId="11" borderId="2" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="169" fontId="21" fillId="11" borderId="2" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="168" fontId="12" fillId="0" borderId="2" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="24" fillId="13" borderId="7" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="25" fillId="0" borderId="7" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="26" fillId="14" borderId="7" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="27" fillId="15" borderId="7" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="9" fillId="0" borderId="7" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="170" fontId="27" fillId="16" borderId="7" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="169" fontId="27" fillId="17" borderId="7" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="27" fillId="17" borderId="7" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="26" fillId="18" borderId="7" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="28" fillId="19" borderId="7" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="10" fillId="20" borderId="7" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="29" fillId="21" borderId="7" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="170" fontId="10" fillId="22" borderId="7" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="170" fontId="10" fillId="0" borderId="7" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="169" fontId="10" fillId="0" borderId="7" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="30" fillId="23" borderId="7" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="31" fillId="19" borderId="7" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="12" fillId="0" borderId="7" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="170" fontId="12" fillId="0" borderId="7" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="10" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="11" pivotButton="0" quotePrefix="0" xfId="0"/>
   </cellXfs>
   <cellStyles count="2">
     <cellStyle name="Normal" xfId="0" builtinId="0"/>
@@ -943,7 +1128,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:T2"/>
+  <dimension ref="A1:T3"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="17" customWidth="1" min="1" max="1"/>
@@ -1115,13 +1300,62 @@
         </is>
       </c>
       <c r="S2" s="80" t="n">
-        <v>2.5</v>
+        <v>1.05</v>
       </c>
       <c r="T2" s="80" t="n">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="3" ht="15.75" customHeight="1"/>
+        <v>145</v>
+      </c>
+    </row>
+    <row r="3" ht="15.75" customHeight="1">
+      <c r="A3" t="inlineStr">
+        <is>
+          <t>Sold Put</t>
+        </is>
+      </c>
+      <c r="B3" s="39" t="inlineStr">
+        <is>
+          <t>10/17/2025</t>
+        </is>
+      </c>
+      <c r="C3" s="80" t="n">
+        <v>56</v>
+      </c>
+      <c r="D3" t="inlineStr">
+        <is>
+          <t>AVL</t>
+        </is>
+      </c>
+      <c r="E3" s="39" t="inlineStr">
+        <is>
+          <t>9/5/2025</t>
+        </is>
+      </c>
+      <c r="F3" t="n">
+        <v>-200</v>
+      </c>
+      <c r="G3" s="80" t="n">
+        <v>4.5</v>
+      </c>
+      <c r="I3" s="81" t="inlineStr"/>
+      <c r="K3" s="80" t="n">
+        <v>900</v>
+      </c>
+      <c r="L3" s="80" t="n">
+        <v>11200</v>
+      </c>
+      <c r="M3" t="inlineStr">
+        <is>
+          <t>Sold based on wishlist recommendation</t>
+        </is>
+      </c>
+      <c r="N3" s="39" t="inlineStr"/>
+      <c r="S3" s="80" t="n">
+        <v>5.2</v>
+      </c>
+      <c r="T3" s="80" t="n">
+        <v>-140</v>
+      </c>
+    </row>
     <row r="4" ht="15.75" customHeight="1"/>
     <row r="5" ht="15.75" customHeight="1"/>
     <row r="6" ht="15.75" customHeight="1"/>
@@ -2971,366 +3205,317 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:G40"/>
+  <dimension ref="A1:G37"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="25" customWidth="1" min="1" max="1"/>
-    <col width="22" customWidth="1" min="2" max="2"/>
-    <col width="21" customWidth="1" min="3" max="3"/>
-    <col width="20" customWidth="1" min="4" max="4"/>
+    <col width="11" customWidth="1" min="2" max="2"/>
+    <col width="15" customWidth="1" min="3" max="3"/>
+    <col width="15" customWidth="1" min="4" max="4"/>
     <col width="18" customWidth="1" min="5" max="5"/>
     <col width="6" customWidth="1" min="6" max="6"/>
   </cols>
   <sheetData>
-    <row r="1" ht="26.25" customHeight="1">
-      <c r="A1" s="75" t="inlineStr">
+    <row r="1">
+      <c r="A1" s="97" t="inlineStr">
         <is>
           <t>🏆 TRADING RESULTS DASHBOARD</t>
         </is>
       </c>
-      <c r="B1" s="73" t="n"/>
-      <c r="C1" s="73" t="n"/>
-      <c r="D1" s="73" t="n"/>
-      <c r="E1" s="73" t="n"/>
-      <c r="F1" s="73" t="n"/>
-      <c r="G1" s="74" t="n"/>
+      <c r="B1" s="116" t="n"/>
+      <c r="C1" s="116" t="n"/>
+      <c r="D1" s="116" t="n"/>
+      <c r="E1" s="116" t="n"/>
+      <c r="F1" s="116" t="n"/>
+      <c r="G1" s="117" t="n"/>
     </row>
     <row r="2">
-      <c r="A2" s="78" t="inlineStr">
-        <is>
-          <t>Generated: 08/15/2025 08:15 AM</t>
-        </is>
-      </c>
-      <c r="B2" s="73" t="n"/>
-      <c r="C2" s="73" t="n"/>
-      <c r="D2" s="73" t="n"/>
-      <c r="E2" s="73" t="n"/>
-      <c r="F2" s="73" t="n"/>
-      <c r="G2" s="74" t="n"/>
-    </row>
-    <row r="5" ht="20.25" customHeight="1">
-      <c r="A5" s="79" t="inlineStr">
+      <c r="A2" s="98" t="inlineStr">
+        <is>
+          <t>Generated: 09/05/2025 10:00 AM</t>
+        </is>
+      </c>
+      <c r="B2" s="116" t="n"/>
+      <c r="C2" s="116" t="n"/>
+      <c r="D2" s="116" t="n"/>
+      <c r="E2" s="116" t="n"/>
+      <c r="F2" s="116" t="n"/>
+      <c r="G2" s="117" t="n"/>
+    </row>
+    <row r="5">
+      <c r="A5" s="99" t="inlineStr">
         <is>
           <t>📈 CLOSED TRADES PERFORMANCE</t>
         </is>
       </c>
-      <c r="B5" s="73" t="n"/>
-      <c r="C5" s="73" t="n"/>
-      <c r="D5" s="73" t="n"/>
-      <c r="E5" s="74" t="n"/>
-    </row>
-    <row r="7" ht="15.75" customHeight="1">
-      <c r="A7" s="52" t="inlineStr">
+      <c r="B5" s="116" t="n"/>
+      <c r="C5" s="116" t="n"/>
+      <c r="D5" s="116" t="n"/>
+      <c r="E5" s="117" t="n"/>
+    </row>
+    <row r="7">
+      <c r="A7" s="100" t="inlineStr">
         <is>
           <t>Year</t>
         </is>
       </c>
-      <c r="B7" s="52" t="inlineStr">
+      <c r="B7" s="100" t="inlineStr">
         <is>
           <t>Total P&amp;L</t>
         </is>
       </c>
-      <c r="C7" s="52" t="inlineStr">
+      <c r="C7" s="100" t="inlineStr">
         <is>
           <t>Average P&amp;L %</t>
         </is>
       </c>
-      <c r="D7" s="52" t="inlineStr">
+      <c r="D7" s="100" t="inlineStr">
         <is>
           <t>Win Rate</t>
         </is>
       </c>
-      <c r="E7" s="52" t="inlineStr">
+      <c r="E7" s="100" t="inlineStr">
         <is>
           <t>Number of Trades</t>
         </is>
       </c>
     </row>
     <row r="8">
-      <c r="A8" s="53" t="n">
-        <v>2025</v>
-      </c>
-      <c r="B8" s="87" t="n">
-        <v>32219.5</v>
-      </c>
-      <c r="C8" s="88" t="n">
-        <v>0.2017521126760564</v>
-      </c>
-      <c r="D8" s="89" t="n">
-        <v>0.9014084507042254</v>
-      </c>
-      <c r="E8" s="57" t="n">
-        <v>71</v>
-      </c>
-    </row>
-    <row r="9" ht="15.75" customHeight="1">
-      <c r="A9" s="58" t="inlineStr">
+      <c r="A8" s="101" t="inlineStr">
         <is>
           <t>TOTAL</t>
         </is>
       </c>
-      <c r="B9" s="90" t="n">
-        <v>32219.5</v>
-      </c>
-      <c r="C9" s="91" t="n">
-        <v>0.2017521126760564</v>
-      </c>
-      <c r="D9" s="91" t="n">
-        <v>0.9014084507042254</v>
-      </c>
-      <c r="E9" s="61" t="n">
-        <v>71</v>
-      </c>
-    </row>
-    <row r="13" ht="20.25" customHeight="1">
-      <c r="A13" s="76" t="inlineStr">
+      <c r="B8" s="102" t="n">
+        <v>0</v>
+      </c>
+      <c r="C8" s="103" t="n">
+        <v>0</v>
+      </c>
+      <c r="D8" s="103" t="n">
+        <v>0</v>
+      </c>
+      <c r="E8" s="104" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="12">
+      <c r="A12" s="105" t="inlineStr">
         <is>
           <t>📊 OPEN TRADES SUMMARY (REAL-TIME)</t>
         </is>
       </c>
-      <c r="B13" s="73" t="n"/>
-      <c r="C13" s="73" t="n"/>
-      <c r="D13" s="73" t="n"/>
-      <c r="E13" s="73" t="n"/>
-      <c r="F13" s="74" t="n"/>
-    </row>
-    <row r="15" ht="16.5" customHeight="1">
-      <c r="A15" s="72" t="inlineStr">
+      <c r="B12" s="116" t="n"/>
+      <c r="C12" s="116" t="n"/>
+      <c r="D12" s="116" t="n"/>
+      <c r="E12" s="116" t="n"/>
+      <c r="F12" s="117" t="n"/>
+    </row>
+    <row r="14">
+      <c r="A14" s="106" t="inlineStr">
         <is>
           <t>📊 Portfolio Overview</t>
         </is>
       </c>
-      <c r="B15" s="73" t="n"/>
-      <c r="C15" s="74" t="n"/>
+      <c r="B14" s="116" t="n"/>
+      <c r="C14" s="117" t="n"/>
+    </row>
+    <row r="15">
+      <c r="A15" s="107" t="inlineStr">
+        <is>
+          <t>Number of Open Trades</t>
+        </is>
+      </c>
+      <c r="B15" s="108" t="n">
+        <v>2</v>
+      </c>
     </row>
     <row r="16">
-      <c r="A16" s="62" t="inlineStr">
-        <is>
-          <t>Number of Open Trades</t>
-        </is>
-      </c>
-      <c r="B16" s="63" t="n">
-        <v>30</v>
-      </c>
-    </row>
-    <row r="17">
-      <c r="A17" s="62" t="inlineStr">
+      <c r="A16" s="107" t="inlineStr">
         <is>
           <t>Total Cash Investment</t>
         </is>
       </c>
-      <c r="B17" s="92" t="n">
-        <v>134583.4</v>
-      </c>
-    </row>
-    <row r="19" ht="16.5" customHeight="1">
-      <c r="A19" s="72" t="inlineStr">
+      <c r="B16" s="109" t="n">
+        <v>14800</v>
+      </c>
+    </row>
+    <row r="18">
+      <c r="A18" s="106" t="inlineStr">
         <is>
           <t>💰 Option Values</t>
         </is>
       </c>
-      <c r="B19" s="73" t="n"/>
-      <c r="C19" s="74" t="n"/>
+      <c r="B18" s="116" t="n"/>
+      <c r="C18" s="117" t="n"/>
+    </row>
+    <row r="19">
+      <c r="A19" s="107" t="inlineStr">
+        <is>
+          <t>Total Call Value</t>
+        </is>
+      </c>
+      <c r="B19" s="110" t="n">
+        <v>0</v>
+      </c>
     </row>
     <row r="20">
-      <c r="A20" s="62" t="inlineStr">
-        <is>
-          <t>Total Call Value</t>
-        </is>
-      </c>
-      <c r="B20" s="93" t="n">
+      <c r="A20" s="107" t="inlineStr">
+        <is>
+          <t>Total Put Value</t>
+        </is>
+      </c>
+      <c r="B20" s="109" t="n">
+        <v>1150</v>
+      </c>
+    </row>
+    <row r="21">
+      <c r="A21" s="107" t="inlineStr">
+        <is>
+          <t>Cash at Risk (Put Req.)</t>
+        </is>
+      </c>
+      <c r="B21" s="109" t="n">
+        <v>14800</v>
+      </c>
+    </row>
+    <row r="23">
+      <c r="A23" s="106" t="inlineStr">
+        <is>
+          <t>📈 Current Performance</t>
+        </is>
+      </c>
+      <c r="B23" s="116" t="n"/>
+      <c r="C23" s="117" t="n"/>
+    </row>
+    <row r="24">
+      <c r="A24" s="107" t="inlineStr">
+        <is>
+          <t>Current Unrealized P&amp;L</t>
+        </is>
+      </c>
+      <c r="B24" s="110" t="n">
         <v>0</v>
       </c>
     </row>
-    <row r="21">
-      <c r="A21" s="62" t="inlineStr">
-        <is>
-          <t>Total Put Value</t>
-        </is>
-      </c>
-      <c r="B21" s="92" t="n">
-        <v>5435</v>
-      </c>
-    </row>
-    <row r="22">
-      <c r="A22" s="62" t="inlineStr">
-        <is>
-          <t>Cash at Risk (Put Req.)</t>
-        </is>
-      </c>
-      <c r="B22" s="92" t="n">
-        <v>32800</v>
-      </c>
-    </row>
-    <row r="24" ht="16.5" customHeight="1">
-      <c r="A24" s="72" t="inlineStr">
-        <is>
-          <t>📈 Current Performance</t>
-        </is>
-      </c>
-      <c r="B24" s="73" t="n"/>
-      <c r="C24" s="74" t="n"/>
-    </row>
     <row r="25">
-      <c r="A25" s="62" t="inlineStr">
-        <is>
-          <t>Current Unrealized P&amp;L</t>
-        </is>
-      </c>
-      <c r="B25" s="94" t="n">
-        <v>-25850</v>
+      <c r="A25" s="107" t="inlineStr">
+        <is>
+          <t>Current P&amp;L %</t>
+        </is>
+      </c>
+      <c r="B25" s="111" t="n">
+        <v>0</v>
       </c>
     </row>
     <row r="26">
-      <c r="A26" s="62" t="inlineStr">
-        <is>
-          <t>Current P&amp;L %</t>
-        </is>
-      </c>
-      <c r="B26" s="95" t="n">
-        <v>-0.1920742082604541</v>
-      </c>
-    </row>
-    <row r="27">
-      <c r="A27" s="62" t="inlineStr">
+      <c r="A26" s="107" t="inlineStr">
         <is>
           <t>Portfolio Value</t>
         </is>
       </c>
-      <c r="B27" s="92" t="n">
-        <v>108733.4</v>
-      </c>
-    </row>
-    <row r="29" ht="16.5" customHeight="1">
-      <c r="A29" s="72" t="inlineStr">
+      <c r="B26" s="109" t="n">
+        <v>14800</v>
+      </c>
+    </row>
+    <row r="28">
+      <c r="A28" s="106" t="inlineStr">
         <is>
           <t>🎯 Risk Metrics</t>
         </is>
       </c>
-      <c r="B29" s="73" t="n"/>
-      <c r="C29" s="74" t="n"/>
+      <c r="B28" s="116" t="n"/>
+      <c r="C28" s="117" t="n"/>
+    </row>
+    <row r="29">
+      <c r="A29" s="107" t="inlineStr">
+        <is>
+          <t>Total Exposure</t>
+        </is>
+      </c>
+      <c r="B29" s="109" t="n">
+        <v>29600</v>
+      </c>
     </row>
     <row r="30">
-      <c r="A30" s="62" t="inlineStr">
-        <is>
-          <t>Total Exposure</t>
-        </is>
-      </c>
-      <c r="B30" s="92" t="n">
-        <v>167383.4</v>
+      <c r="A30" s="107" t="inlineStr">
+        <is>
+          <t>Options Premium Value</t>
+        </is>
+      </c>
+      <c r="B30" s="109" t="n">
+        <v>1150</v>
       </c>
     </row>
     <row r="31">
-      <c r="A31" s="62" t="inlineStr">
-        <is>
-          <t>Options Premium Value</t>
-        </is>
-      </c>
-      <c r="B31" s="92" t="n">
-        <v>5435</v>
-      </c>
-    </row>
-    <row r="32">
-      <c r="A32" s="62" t="inlineStr">
+      <c r="A31" s="107" t="inlineStr">
         <is>
           <t>Net Liquidity</t>
         </is>
       </c>
-      <c r="B32" s="93" t="n">
-        <v>-27365</v>
-      </c>
-    </row>
-    <row r="35" ht="18" customHeight="1">
-      <c r="A35" s="77" t="inlineStr">
+      <c r="B31" s="110" t="n">
+        <v>-13650</v>
+      </c>
+    </row>
+    <row r="34">
+      <c r="A34" s="112" t="inlineStr">
         <is>
           <t>📋 POSITION TYPE BREAKDOWN</t>
         </is>
       </c>
-      <c r="B35" s="73" t="n"/>
-      <c r="C35" s="73" t="n"/>
-      <c r="D35" s="74" t="n"/>
+      <c r="B34" s="116" t="n"/>
+      <c r="C34" s="116" t="n"/>
+      <c r="D34" s="117" t="n"/>
+    </row>
+    <row r="36">
+      <c r="A36" s="113" t="inlineStr">
+        <is>
+          <t>Position Type</t>
+        </is>
+      </c>
+      <c r="B36" s="113" t="inlineStr">
+        <is>
+          <t>Count</t>
+        </is>
+      </c>
+      <c r="C36" s="113" t="inlineStr">
+        <is>
+          <t>Investment</t>
+        </is>
+      </c>
+      <c r="D36" s="113" t="inlineStr">
+        <is>
+          <t>Current Value</t>
+        </is>
+      </c>
     </row>
     <row r="37">
-      <c r="A37" s="68" t="inlineStr">
-        <is>
-          <t>Position Type</t>
-        </is>
-      </c>
-      <c r="B37" s="68" t="inlineStr">
-        <is>
-          <t>Count</t>
-        </is>
-      </c>
-      <c r="C37" s="68" t="inlineStr">
-        <is>
-          <t>Investment</t>
-        </is>
-      </c>
-      <c r="D37" s="68" t="inlineStr">
-        <is>
-          <t>Current Value</t>
-        </is>
-      </c>
-    </row>
-    <row r="38">
-      <c r="A38" s="69" t="inlineStr">
-        <is>
-          <t>Bought Stock</t>
-        </is>
-      </c>
-      <c r="B38" s="69" t="n">
-        <v>13</v>
-      </c>
-      <c r="C38" s="96" t="n">
-        <v>58228.4</v>
-      </c>
-      <c r="D38" s="96" t="n">
+      <c r="A37" s="114" t="inlineStr">
+        <is>
+          <t>Sold Put</t>
+        </is>
+      </c>
+      <c r="B37" s="114" t="n">
+        <v>2</v>
+      </c>
+      <c r="C37" s="115" t="n">
         <v>0</v>
       </c>
-    </row>
-    <row r="39">
-      <c r="A39" s="69" t="inlineStr">
-        <is>
-          <t>Sold Put</t>
-        </is>
-      </c>
-      <c r="B39" s="69" t="n">
-        <v>16</v>
-      </c>
-      <c r="C39" s="96" t="n">
-        <v>43555</v>
-      </c>
-      <c r="D39" s="96" t="n">
-        <v>5980</v>
-      </c>
-    </row>
-    <row r="40">
-      <c r="A40" s="69" t="inlineStr">
-        <is>
-          <t>Bought Put</t>
-        </is>
-      </c>
-      <c r="B40" s="69" t="n">
-        <v>1</v>
-      </c>
-      <c r="C40" s="96" t="n">
-        <v>0</v>
-      </c>
-      <c r="D40" s="96" t="n">
-        <v>-545</v>
+      <c r="D37" s="115" t="n">
+        <v>1150</v>
       </c>
     </row>
   </sheetData>
   <mergeCells count="9">
-    <mergeCell ref="A19:C19"/>
+    <mergeCell ref="A28:C28"/>
     <mergeCell ref="A1:G1"/>
-    <mergeCell ref="A13:F13"/>
-    <mergeCell ref="A35:D35"/>
+    <mergeCell ref="A23:C23"/>
+    <mergeCell ref="A34:D34"/>
+    <mergeCell ref="A14:C14"/>
+    <mergeCell ref="A18:C18"/>
     <mergeCell ref="A2:G2"/>
     <mergeCell ref="A5:E5"/>
-    <mergeCell ref="A15:C15"/>
-    <mergeCell ref="A24:C24"/>
-    <mergeCell ref="A29:C29"/>
+    <mergeCell ref="A12:F12"/>
   </mergeCells>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
